--- a/bin/Debug/net8.0-windows/XYZ.xlsx
+++ b/bin/Debug/net8.0-windows/XYZ.xlsx
@@ -33,6 +33,24 @@
   <x:si>
     <x:t>Short Description</x:t>
   </x:si>
+  <x:si>
+    <x:t>2026-04-14 03:23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>atanu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Testing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INC12345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InProgress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Just Testing</x:t>
+  </x:si>
 </x:sst>
 </file>
 
@@ -41,7 +59,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -54,6 +72,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -90,21 +115,28 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -433,6 +465,26 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:6">
+      <x:c r="A2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
